--- a/数据表/Datas/SpriteConfig_图片资源.xlsx
+++ b/数据表/Datas/SpriteConfig_图片资源.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16080"/>
+    <workbookView windowHeight="16060"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
   <si>
     <t>##var</t>
   </si>
@@ -103,24 +103,30 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Sprite </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>索引（</t>
-    </r>
-    <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
         <rFont val="Andale Mono"/>
         <charset val="134"/>
       </rPr>
+      <t xml:space="preserve">Sprite </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>索引（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">-1 </t>
     </r>
     <r>
@@ -135,6 +141,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>##</t>
     </r>
     <r>
@@ -151,6 +162,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>角色</t>
     </r>
     <r>
@@ -236,6 +253,95 @@
         <rFont val="宋体-简"/>
         <charset val="134"/>
       </rPr>
+      <t>敌人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>素材</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <t>Monsters.png</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>##</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体-简"/>
+        <charset val="134"/>
+      </rPr>
       <t>道具素材</t>
     </r>
   </si>
@@ -287,15 +393,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>神秘遗物</t>
-    </r>
+    <t>神秘遗物</t>
   </si>
   <si>
     <r>
@@ -563,22 +661,22 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="PingFang SC Regular"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体-简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF9C0006"/>
       <name val="PingFang SC Regular"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体-简"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="37">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -630,18 +728,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -919,7 +1005,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -985,90 +1071,90 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1104,18 +1190,11 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center"/>
@@ -1591,7 +1670,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12.625" style="1" customWidth="1"/>
@@ -1658,18 +1737,18 @@
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:4">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:4">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="2">
@@ -1677,10 +1756,10 @@
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:4">
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="2">
@@ -1688,10 +1767,10 @@
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:4">
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D8" s="2">
@@ -1699,10 +1778,10 @@
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:4">
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D9" s="2">
@@ -1710,120 +1789,161 @@
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:4">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="17" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:4">
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="15" t="s">
         <v>22</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D13" s="2">
-        <v>264</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:4">
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="15" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D14" s="2">
-        <v>275</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:4">
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="15" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D15" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:4">
+      <c r="B18" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="2">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:4">
+      <c r="B19" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="2">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:4">
+      <c r="B20" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="2">
         <v>176</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:4">
-      <c r="B16" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" s="2">
+    <row r="21" customHeight="1" spans="1:4">
+      <c r="B21" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="2">
         <v>238</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="2:4">
-      <c r="B17" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="2">
+    <row r="22" customHeight="1" spans="1:4">
+      <c r="B22" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="2">
         <v>182</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="2:4">
-      <c r="B18" s="18" t="s">
+    <row r="23" customHeight="1" spans="1:4">
+      <c r="B23" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="2">
+      <c r="D23" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="2:4">
-      <c r="B19" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="2">
+    <row r="24" customHeight="1" spans="1:4">
+      <c r="B24" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="2">
         <v>110</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="2:4">
-      <c r="B20" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="2">
+    <row r="25" customHeight="1" spans="1:4">
+      <c r="B25" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="2">
         <v>132</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="2:4">
-      <c r="B21" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="2">
+    <row r="26" customHeight="1" spans="1:4">
+      <c r="B26" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="2">
         <v>134</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="2:4">
-      <c r="B22" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="2">
+    <row r="27" customHeight="1" spans="1:4">
+      <c r="B27" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="2">
         <v>220</v>
       </c>
     </row>

--- a/数据表/Datas/SpriteConfig_图片资源.xlsx
+++ b/数据表/Datas/SpriteConfig_图片资源.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16060"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="58">
   <si>
     <t>##var</t>
   </si>
@@ -245,6 +245,231 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>13</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>14</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>15</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>##</t>
     </r>
     <r>
@@ -325,6 +550,186 @@
         <charset val="134"/>
       </rPr>
       <t>3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>12</t>
     </r>
   </si>
   <si>
@@ -661,12 +1066,12 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="宋体-简"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体-简"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1670,7 +2075,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12.625" style="1" customWidth="1"/>
@@ -1788,162 +2193,388 @@
         <v>3</v>
       </c>
     </row>
+    <row r="10" customHeight="1" spans="1:4">
+      <c r="B10" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:4">
+      <c r="B11" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="2">
+        <v>5</v>
+      </c>
+    </row>
     <row r="12" customHeight="1" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>15</v>
+      <c r="B12" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="2">
+        <v>6</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:4">
-      <c r="B13" s="15" t="s">
-        <v>22</v>
+      <c r="B13" s="16" t="s">
+        <v>24</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D13" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:4">
       <c r="B14" s="15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D14" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:4">
-      <c r="B15" s="15" t="s">
-        <v>25</v>
+      <c r="B15" s="16" t="s">
+        <v>26</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D15" s="2">
-        <v>2</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:4">
+      <c r="B16" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="2">
+        <v>10</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:4">
-      <c r="A17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>15</v>
+      <c r="B17" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="2">
+        <v>11</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:4">
-      <c r="B18" s="16" t="s">
-        <v>27</v>
+      <c r="B18" s="15" t="s">
+        <v>29</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D18" s="2">
-        <v>264</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:4">
       <c r="B19" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D19" s="2">
-        <v>275</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:4">
       <c r="B20" s="16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D20" s="2">
-        <v>176</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:4">
-      <c r="B21" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="2">
-        <v>238</v>
-      </c>
+      <c r="B21" s="16"/>
     </row>
     <row r="22" customHeight="1" spans="1:4">
-      <c r="B22" s="15" t="s">
+      <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="2">
-        <v>182</v>
+      <c r="B22" s="17" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:4">
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="15" t="s">
         <v>33</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:4">
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="D24" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:4">
+      <c r="B25" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:4">
+      <c r="B26" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:4">
+      <c r="B27" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:4">
+      <c r="B28" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:4">
+      <c r="B29" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:4">
+      <c r="B30" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:4">
+      <c r="B31" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:4">
+      <c r="B32" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:4">
+      <c r="B33" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:4">
+      <c r="B34" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:4">
+      <c r="B35" s="15"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:4">
+      <c r="A37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:4">
+      <c r="B38" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" s="2">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:4">
+      <c r="B39" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D39" s="2">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:4">
+      <c r="B40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D40" s="2">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:4">
+      <c r="B41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D41" s="2">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="1:4">
+      <c r="B42" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D42" s="2">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="1:4">
+      <c r="B43" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="1:4">
+      <c r="B44" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D44" s="2">
         <v>110</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:4">
-      <c r="B25" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" s="2">
+    <row r="45" customHeight="1" spans="1:4">
+      <c r="B45" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D45" s="2">
         <v>132</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:4">
-      <c r="B26" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="2">
+    <row r="46" customHeight="1" spans="1:4">
+      <c r="B46" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D46" s="2">
         <v>134</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:4">
-      <c r="B27" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" s="2">
+    <row r="47" customHeight="1" spans="1:4">
+      <c r="B47" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D47" s="2">
         <v>220</v>
       </c>
     </row>

--- a/数据表/Datas/SpriteConfig_图片资源.xlsx
+++ b/数据表/Datas/SpriteConfig_图片资源.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\Seek-Battle-Evacuate\数据表\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="134">
   <si>
     <t>##var</t>
   </si>
@@ -66,7 +71,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>资源键</t>
@@ -77,7 +82,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>图集路径（相对于</t>
@@ -86,7 +91,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> Assets/GameMain/Textures</t>
@@ -95,7 +100,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>）</t>
@@ -103,37 +108,31 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">Sprite </t>
+    </r>
+    <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">Sprite </t>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>索引（</t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>索引（</t>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">-1 </t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">-1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>表示整张图）</t>
@@ -141,17 +140,12 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
       <t>##</t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色素材</t>
@@ -165,7 +159,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -174,7 +168,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -188,7 +182,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -197,7 +191,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>2</t>
@@ -208,7 +202,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -217,7 +211,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>3</t>
@@ -228,7 +222,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -237,7 +231,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>4</t>
@@ -248,7 +242,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -257,7 +251,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>5</t>
@@ -268,7 +262,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -277,7 +271,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>6</t>
@@ -288,7 +282,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -297,7 +291,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>7</t>
@@ -308,7 +302,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -317,7 +311,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>8</t>
@@ -328,7 +322,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -337,7 +331,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>9</t>
@@ -348,7 +342,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -357,7 +351,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>10</t>
@@ -368,7 +362,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -377,7 +371,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>11</t>
@@ -388,7 +382,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -397,7 +391,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>12</t>
@@ -408,7 +402,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -417,7 +411,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>13</t>
@@ -428,7 +422,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -437,7 +431,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>14</t>
@@ -448,7 +442,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>角色</t>
@@ -457,7 +451,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>15</t>
@@ -465,17 +459,23 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
       <t>##</t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="宋体-简"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人素材</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人</t>
@@ -483,18 +483,22 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>素材</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <t>Monsters.png</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人</t>
@@ -503,21 +507,18 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <t>Monsters.png</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人</t>
@@ -526,18 +527,18 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人</t>
@@ -546,18 +547,18 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人</t>
@@ -566,18 +567,18 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人</t>
@@ -586,18 +587,18 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人</t>
@@ -606,18 +607,18 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>6</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人</t>
@@ -626,18 +627,18 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>7</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人</t>
@@ -646,18 +647,18 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>8</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人</t>
@@ -666,18 +667,18 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>9</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人</t>
@@ -686,18 +687,18 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>10</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人</t>
@@ -706,27 +707,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>11</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>敌人</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>12</t>
@@ -734,31 +715,42 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
       <t>##</t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="宋体-简"/>
-        <charset val="134"/>
-      </rPr>
-      <t>道具素材</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>旧硬币</t>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>道具</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>常规</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>铜币</t>
     </r>
   </si>
   <si>
@@ -769,91 +761,1614 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>宝石碎片</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>古代零件</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>精致核心</t>
-    </r>
-  </si>
-  <si>
-    <t>神秘遗物</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>训练剑</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>法杖</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>布甲</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>银币</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>金币</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>铂币</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>全币</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>骨头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>骨头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>骨头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>骨头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>骨头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> V</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>骨头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VI</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>骨头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>骨头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VIII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>骨头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IX</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>符文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>符文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>符文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>符文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>符文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> V</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>符文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VI</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>符文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>符文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VIII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>符文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IX</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>种子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>种子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>种子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>种子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>种子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> V</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>种子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VI</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>种子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>种子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VIII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>种子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IX</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宝石</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宝石</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宝石</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宝石</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宝石</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> V</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宝石</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VI</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宝石</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宝石</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VIII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宝石</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IX</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>收集品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>收集品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>收集品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>收集品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>收集品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> V</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>收集品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VI</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>收集品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>收集品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VIII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>收集品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IX</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>##</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>道具</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>武器</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>短剑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>短剑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>短剑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>菜刀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>菜刀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>菜刀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>阔剑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>阔剑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>阔剑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小法杖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小法杖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小法杖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中法杖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中法杖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中法杖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大法杖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大法杖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大法杖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>##</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>道具</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>防具</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头盔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头盔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头盔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头盔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头盔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> V</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>术士长袍</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>恢复药</t>
-    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>术士长袍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>术士长袍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>术士长袍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>术士长袍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> V</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>##</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>道具</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>消耗品</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小药</t>
+    </r>
+  </si>
+  <si>
+    <t>中小药</t>
+  </si>
+  <si>
+    <t>中药</t>
+  </si>
+  <si>
+    <t>中大药</t>
+  </si>
+  <si>
+    <t>大药</t>
   </si>
 </sst>
 </file>
@@ -874,43 +2389,42 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF006100"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F4E78"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF595959"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF202020"/>
-      <name val="PingFang SC Regular"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF202020"/>
-      <name val="Andale Mono"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1066,18 +2580,19 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="宋体-简"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="PingFang SC Regular"/>
+      <color rgb="FF202020"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
-      <name val="PingFang SC Regular"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1598,8 +3113,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center"/>
@@ -2075,13 +3590,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D145"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="12.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.6911764705882" style="2" customWidth="1"/>
-    <col min="3" max="3" width="56.8602941176471" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.7720588235294" style="2" customWidth="1"/>
+    <col min="1" max="1" width="16.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.6916666666667" style="2" customWidth="1"/>
+    <col min="3" max="3" width="48.5833333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.75" style="2" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -2161,7 +3676,7 @@
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:4">
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -2172,7 +3687,7 @@
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:4">
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -2183,7 +3698,7 @@
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:4">
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="15" t="s">
         <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -2205,7 +3720,7 @@
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:4">
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="15" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -2216,7 +3731,7 @@
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:4">
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="15" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -2227,7 +3742,7 @@
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:4">
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="15" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -2249,7 +3764,7 @@
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:4">
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="15" t="s">
         <v>26</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -2260,7 +3775,7 @@
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:4">
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="15" t="s">
         <v>27</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -2271,7 +3786,7 @@
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:4">
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="15" t="s">
         <v>28</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -2293,7 +3808,7 @@
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:4">
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="15" t="s">
         <v>30</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -2304,7 +3819,7 @@
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:4">
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="15" t="s">
         <v>31</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -2315,7 +3830,7 @@
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:4">
-      <c r="B21" s="16"/>
+      <c r="B21" s="15"/>
     </row>
     <row r="22" customHeight="1" spans="1:4">
       <c r="A22" s="1" t="s">
@@ -2469,47 +3984,47 @@
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:4">
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="15" t="s">
         <v>47</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D38" s="2">
-        <v>264</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:4">
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="15" t="s">
         <v>49</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D39" s="2">
-        <v>275</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:4">
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="15" t="s">
         <v>50</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D40" s="2">
-        <v>176</v>
+        <v>130</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:4">
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="15" t="s">
         <v>51</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>48</v>
       </c>
       <c r="D41" s="2">
-        <v>238</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:4">
@@ -2520,62 +4035,949 @@
         <v>48</v>
       </c>
       <c r="D42" s="2">
-        <v>182</v>
+        <v>132</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:4">
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="15"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:4">
+      <c r="B44" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D43" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="1:4">
-      <c r="B44" s="16" t="s">
+      <c r="C44" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D44" s="2">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="1:4">
+      <c r="B45" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D44" s="2">
+      <c r="C45" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D45" s="2">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="1:4">
+      <c r="B46" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D46" s="2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="1:4">
+      <c r="B47" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D47" s="2">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="1:4">
+      <c r="B48" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D48" s="2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="2:4">
+      <c r="B49" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D49" s="2">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="2:4">
+      <c r="B50" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D50" s="2">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="2:4">
+      <c r="B51" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D51" s="2">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="2:4">
+      <c r="B52" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D52" s="2">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="2:4">
+      <c r="B53" s="15"/>
+    </row>
+    <row r="54" customHeight="1" spans="2:4">
+      <c r="B54" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D54" s="2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="2:4">
+      <c r="B55" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D55" s="2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="2:4">
+      <c r="B56" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D56" s="2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="2:4">
+      <c r="B57" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D57" s="2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="2:4">
+      <c r="B58" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D58" s="2">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="2:4">
+      <c r="B59" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D59" s="2">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="2:4">
+      <c r="B60" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D60" s="2">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="2:4">
+      <c r="B61" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D61" s="2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="2:4">
+      <c r="B62" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D62" s="2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="2:4">
+      <c r="B63" s="15"/>
+    </row>
+    <row r="64" customHeight="1" spans="2:4">
+      <c r="B64" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D64" s="2">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="2:4">
+      <c r="B65" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D65" s="2">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="2:4">
+      <c r="B66" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D66" s="2">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="2:4">
+      <c r="B67" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D67" s="2">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="2:4">
+      <c r="B68" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D68" s="2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="2:4">
+      <c r="B69" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D69" s="2">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="2:4">
+      <c r="B70" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D70" s="2">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="2:4">
+      <c r="B71" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D71" s="2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="2:4">
+      <c r="B72" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D72" s="2">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="2:4">
+      <c r="B73" s="15"/>
+    </row>
+    <row r="74" customHeight="1" spans="2:4">
+      <c r="B74" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D74" s="2">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="2:4">
+      <c r="B75" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D75" s="2">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="2:4">
+      <c r="B76" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D76" s="2">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="2:4">
+      <c r="B77" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D77" s="2">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="2:4">
+      <c r="B78" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D78" s="2">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="2:4">
+      <c r="B79" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D79" s="2">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="2:4">
+      <c r="B80" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D80" s="2">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="2:4">
+      <c r="B81" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D81" s="2">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="2:4">
+      <c r="B82" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D82" s="2">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="2:4">
+      <c r="B83" s="15"/>
+    </row>
+    <row r="84" customHeight="1" spans="2:4">
+      <c r="B84" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D84" s="2">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="2:4">
+      <c r="B85" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D85" s="2">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="2:4">
+      <c r="B86" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D86" s="2">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="2:4">
+      <c r="B87" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D87" s="2">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="2:4">
+      <c r="B88" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D88" s="2">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="2:4">
+      <c r="B89" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D89" s="2">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="2:4">
+      <c r="B90" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D90" s="2">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="2:4">
+      <c r="B91" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D91" s="2">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="2:4">
+      <c r="B92" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D92" s="2">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="2:4">
+      <c r="B93" s="15"/>
+    </row>
+    <row r="94" customHeight="1" spans="2:4">
+      <c r="B94" s="15"/>
+    </row>
+    <row r="95" customHeight="1" spans="2:4">
+      <c r="B95" s="15"/>
+    </row>
+    <row r="96" customHeight="1" spans="2:4">
+      <c r="B96" s="15"/>
+    </row>
+    <row r="97" customHeight="1" spans="1:4">
+      <c r="B97" s="15"/>
+    </row>
+    <row r="98" customHeight="1" spans="1:4">
+      <c r="B98" s="15"/>
+    </row>
+    <row r="99" customHeight="1" spans="1:4">
+      <c r="A99" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B99" s="15"/>
+    </row>
+    <row r="100" customHeight="1" spans="1:4">
+      <c r="B100" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D100" s="2">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="1:4">
+      <c r="B101" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D101" s="2">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="1:4">
+      <c r="B102" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D102" s="2">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="1:4">
+      <c r="B103" s="15"/>
+    </row>
+    <row r="104" customHeight="1" spans="1:4">
+      <c r="B104" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D104" s="2">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="1:4">
+      <c r="B105" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D105" s="2">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="1:4">
+      <c r="B106" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D106" s="2">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="1:4">
+      <c r="B107" s="15"/>
+    </row>
+    <row r="108" customHeight="1" spans="1:4">
+      <c r="B108" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D108" s="2">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="1:4">
+      <c r="B109" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D109" s="2">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="1:4">
+      <c r="B110" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D110" s="2">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="1:4">
+      <c r="B111" s="15"/>
+    </row>
+    <row r="112" customHeight="1" spans="1:4">
+      <c r="B112" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D112" s="2">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="1:4">
+      <c r="B113" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D113" s="2">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="1:4">
+      <c r="B114" s="15" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="45" customHeight="1" spans="1:4">
-      <c r="B45" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D45" s="2">
+      <c r="C114" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D114" s="2">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="1:4">
+      <c r="B115" s="15"/>
+    </row>
+    <row r="116" customHeight="1" spans="1:4">
+      <c r="B116" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D116" s="2">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="1:4">
+      <c r="B117" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D117" s="2">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="1:4">
+      <c r="B118" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D118" s="2">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="1:4">
+      <c r="B119" s="15"/>
+    </row>
+    <row r="120" customHeight="1" spans="1:4">
+      <c r="B120" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D120" s="2">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="1:4">
+      <c r="B121" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D121" s="2">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" spans="1:4">
+      <c r="B122" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D122" s="2">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" spans="1:4">
+      <c r="B123" s="15"/>
+    </row>
+    <row r="124" customHeight="1" spans="1:4">
+      <c r="B124" s="15"/>
+    </row>
+    <row r="125" customHeight="1" spans="1:4">
+      <c r="A125" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B125" s="15"/>
+    </row>
+    <row r="126" customHeight="1" spans="1:4">
+      <c r="B126" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D126" s="2">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="1:4">
+      <c r="B127" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D127" s="2">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="1:4">
+      <c r="B128" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D128" s="2">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="1:4">
+      <c r="B129" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D129" s="2">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" spans="1:4">
+      <c r="B130" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D130" s="2">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" spans="1:4">
+      <c r="B131" s="15"/>
+    </row>
+    <row r="132" customHeight="1" spans="1:4">
+      <c r="B132" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D132" s="2">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" spans="1:4">
+      <c r="B133" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D133" s="2">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" spans="1:4">
+      <c r="B134" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D134" s="2">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="135" customHeight="1" spans="1:4">
+      <c r="B135" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D135" s="2">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="136" customHeight="1" spans="1:4">
+      <c r="B136" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D136" s="2">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="137" customHeight="1" spans="1:4">
+      <c r="B137" s="15"/>
+    </row>
+    <row r="138" customHeight="1" spans="1:4">
+      <c r="B138" s="15"/>
+    </row>
+    <row r="139" customHeight="1" spans="1:4">
+      <c r="B139" s="15"/>
+    </row>
+    <row r="140" customHeight="1" spans="1:4">
+      <c r="A140" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B140" s="15"/>
+    </row>
+    <row r="141" customHeight="1" spans="1:4">
+      <c r="B141" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D141" s="2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="142" customHeight="1" spans="1:4">
+      <c r="B142" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D142" s="2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="143" customHeight="1" spans="1:4">
+      <c r="B143" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D143" s="2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="144" customHeight="1" spans="1:4">
+      <c r="B144" s="16" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="46" customHeight="1" spans="1:4">
-      <c r="B46" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D46" s="2">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="1:4">
-      <c r="B47" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D47" s="2">
-        <v>220</v>
+      <c r="C144" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D144" s="2">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" spans="2:4">
+      <c r="B145" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D145" s="2">
+        <v>276</v>
       </c>
     </row>
   </sheetData>
